--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82295688</v>
+        <v>122704516</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
+        <v>95015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,46 +1416,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrskog, Torö, Srm</t>
+          <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664443.1687117612</v>
+        <v>664352</v>
       </c>
       <c r="R8" t="n">
-        <v>6526324.252439899</v>
+        <v>6526273</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,22 +1470,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,22 +1494,600 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122704617</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110382</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torö, Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>664361</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6526241</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122703321</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90851</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Torö, Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>664287</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6526578</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122703218</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94861</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>210</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torö, Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>664296</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6526576</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>82295688</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5113</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrskog, Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>664443.1687117612</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6526324.252439899</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-02-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-02-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Ronny Fors</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Ronny Fors, Anders Tranberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122703885</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90851</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Torö, Torö, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>664452</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6526549</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122703218</v>
+        <v>122703321</v>
       </c>
       <c r="B8" t="n">
-        <v>94964</v>
+        <v>90958</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,50 +1412,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664296</v>
+        <v>664287</v>
       </c>
       <c r="R8" t="n">
-        <v>6526576</v>
+        <v>6526578</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122704617</v>
+        <v>122704516</v>
       </c>
       <c r="B9" t="n">
-        <v>110485</v>
+        <v>95126</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664361</v>
+        <v>664352</v>
       </c>
       <c r="R9" t="n">
-        <v>6526241</v>
+        <v>6526273</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1596,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122704516</v>
+        <v>122703218</v>
       </c>
       <c r="B10" t="n">
-        <v>95118</v>
+        <v>94972</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,37 +1640,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664352</v>
+        <v>664296</v>
       </c>
       <c r="R10" t="n">
-        <v>6526273</v>
+        <v>6526576</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122703321</v>
+        <v>122704617</v>
       </c>
       <c r="B11" t="n">
-        <v>90954</v>
+        <v>110493</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664287</v>
+        <v>664361</v>
       </c>
       <c r="R11" t="n">
-        <v>6526578</v>
+        <v>6526241</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,7 +1982,7 @@
         <v>122703885</v>
       </c>
       <c r="B13" t="n">
-        <v>90954</v>
+        <v>90958</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122703321</v>
+        <v>122704516</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>95126</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664287</v>
+        <v>664352</v>
       </c>
       <c r="R8" t="n">
-        <v>6526578</v>
+        <v>6526273</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122704516</v>
+        <v>122703321</v>
       </c>
       <c r="B9" t="n">
-        <v>95126</v>
+        <v>90958</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,25 +1524,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664352</v>
+        <v>664287</v>
       </c>
       <c r="R9" t="n">
-        <v>6526273</v>
+        <v>6526578</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122704516</v>
+        <v>122704617</v>
       </c>
       <c r="B8" t="n">
-        <v>95126</v>
+        <v>110493</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664352</v>
+        <v>664361</v>
       </c>
       <c r="R8" t="n">
-        <v>6526273</v>
+        <v>6526241</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122703321</v>
+        <v>122703218</v>
       </c>
       <c r="B9" t="n">
-        <v>90958</v>
+        <v>94972</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,41 +1524,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664287</v>
+        <v>664296</v>
       </c>
       <c r="R9" t="n">
-        <v>6526578</v>
+        <v>6526576</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122703218</v>
+        <v>122704516</v>
       </c>
       <c r="B10" t="n">
-        <v>94972</v>
+        <v>95126</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,46 +1649,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664296</v>
+        <v>664352</v>
       </c>
       <c r="R10" t="n">
-        <v>6526576</v>
+        <v>6526273</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122704617</v>
+        <v>122703321</v>
       </c>
       <c r="B11" t="n">
-        <v>110493</v>
+        <v>90958</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664361</v>
+        <v>664287</v>
       </c>
       <c r="R11" t="n">
-        <v>6526241</v>
+        <v>6526578</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122704617</v>
+        <v>122703321</v>
       </c>
       <c r="B8" t="n">
-        <v>110493</v>
+        <v>90958</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664361</v>
+        <v>664287</v>
       </c>
       <c r="R8" t="n">
-        <v>6526241</v>
+        <v>6526578</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122703218</v>
+        <v>122704617</v>
       </c>
       <c r="B9" t="n">
-        <v>94972</v>
+        <v>110495</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,46 +1528,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664296</v>
+        <v>664361</v>
       </c>
       <c r="R9" t="n">
-        <v>6526576</v>
+        <v>6526241</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,7 +1627,7 @@
         <v>122704516</v>
       </c>
       <c r="B10" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1745,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122703321</v>
+        <v>122703218</v>
       </c>
       <c r="B11" t="n">
-        <v>90958</v>
+        <v>94974</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,41 +1748,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664287</v>
+        <v>664296</v>
       </c>
       <c r="R11" t="n">
-        <v>6526578</v>
+        <v>6526576</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122704617</v>
+        <v>122703218</v>
       </c>
       <c r="B9" t="n">
-        <v>110495</v>
+        <v>94974</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,37 +1528,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664361</v>
+        <v>664296</v>
       </c>
       <c r="R9" t="n">
-        <v>6526241</v>
+        <v>6526576</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122704516</v>
+        <v>122704617</v>
       </c>
       <c r="B10" t="n">
-        <v>95128</v>
+        <v>110495</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,21 +1649,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664352</v>
+        <v>664361</v>
       </c>
       <c r="R10" t="n">
-        <v>6526273</v>
+        <v>6526241</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1699,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122703218</v>
+        <v>122704516</v>
       </c>
       <c r="B11" t="n">
-        <v>94974</v>
+        <v>95128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,46 +1761,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664296</v>
+        <v>664352</v>
       </c>
       <c r="R11" t="n">
-        <v>6526576</v>
+        <v>6526273</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122703218</v>
+        <v>122704617</v>
       </c>
       <c r="B9" t="n">
-        <v>94974</v>
+        <v>110495</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,46 +1528,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664296</v>
+        <v>664361</v>
       </c>
       <c r="R9" t="n">
-        <v>6526576</v>
+        <v>6526241</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122704617</v>
+        <v>122703218</v>
       </c>
       <c r="B10" t="n">
-        <v>110495</v>
+        <v>94974</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,37 +1640,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664361</v>
+        <v>664296</v>
       </c>
       <c r="R10" t="n">
-        <v>6526241</v>
+        <v>6526576</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122703321</v>
+        <v>122704516</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>95136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664287</v>
+        <v>664352</v>
       </c>
       <c r="R8" t="n">
-        <v>6526578</v>
+        <v>6526273</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
         <v>122704617</v>
       </c>
       <c r="B9" t="n">
-        <v>110495</v>
+        <v>110503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>122703218</v>
       </c>
       <c r="B10" t="n">
-        <v>94974</v>
+        <v>94982</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122704516</v>
+        <v>122703321</v>
       </c>
       <c r="B11" t="n">
-        <v>95128</v>
+        <v>90966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664352</v>
+        <v>664287</v>
       </c>
       <c r="R11" t="n">
-        <v>6526273</v>
+        <v>6526578</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,7 +1982,7 @@
         <v>122703885</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>90966</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122704516</v>
+        <v>122704617</v>
       </c>
       <c r="B8" t="n">
-        <v>95136</v>
+        <v>110503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664352</v>
+        <v>664361</v>
       </c>
       <c r="R8" t="n">
-        <v>6526273</v>
+        <v>6526241</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122704617</v>
+        <v>122703321</v>
       </c>
       <c r="B9" t="n">
-        <v>110503</v>
+        <v>90966</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,25 +1524,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664361</v>
+        <v>664287</v>
       </c>
       <c r="R9" t="n">
-        <v>6526241</v>
+        <v>6526578</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122703218</v>
+        <v>122704516</v>
       </c>
       <c r="B10" t="n">
-        <v>94982</v>
+        <v>95136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,46 +1640,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664296</v>
+        <v>664352</v>
       </c>
       <c r="R10" t="n">
-        <v>6526576</v>
+        <v>6526273</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122703321</v>
+        <v>122703218</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>94982</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,41 +1748,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664287</v>
+        <v>664296</v>
       </c>
       <c r="R11" t="n">
-        <v>6526578</v>
+        <v>6526576</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122704617</v>
+        <v>122703218</v>
       </c>
       <c r="B8" t="n">
-        <v>110503</v>
+        <v>94982</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,37 +1416,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>664361</v>
+        <v>664296</v>
       </c>
       <c r="R8" t="n">
-        <v>6526241</v>
+        <v>6526576</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122703321</v>
+        <v>122704516</v>
       </c>
       <c r="B9" t="n">
-        <v>90966</v>
+        <v>95136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,25 +1533,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,13 +1561,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664287</v>
+        <v>664352</v>
       </c>
       <c r="R9" t="n">
-        <v>6526578</v>
+        <v>6526273</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122704516</v>
+        <v>122703321</v>
       </c>
       <c r="B10" t="n">
-        <v>95136</v>
+        <v>90966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,25 +1645,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,13 +1673,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664352</v>
+        <v>664287</v>
       </c>
       <c r="R10" t="n">
-        <v>6526273</v>
+        <v>6526578</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1699,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122703218</v>
+        <v>122704617</v>
       </c>
       <c r="B11" t="n">
-        <v>94982</v>
+        <v>110503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,46 +1761,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Torö, Torö, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664296</v>
+        <v>664361</v>
       </c>
       <c r="R11" t="n">
-        <v>6526576</v>
+        <v>6526241</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3220-2020 artfynd.xlsx
+++ b/artfynd/A 3220-2020 artfynd.xlsx
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122703321</v>
+        <v>122704617</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>110503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664287</v>
+        <v>664361</v>
       </c>
       <c r="R10" t="n">
-        <v>6526578</v>
+        <v>6526241</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122704617</v>
+        <v>122703321</v>
       </c>
       <c r="B11" t="n">
-        <v>110503</v>
+        <v>90966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664361</v>
+        <v>664287</v>
       </c>
       <c r="R11" t="n">
-        <v>6526241</v>
+        <v>6526578</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
